--- a/public/exports-60-250/29189617.xlsx
+++ b/public/exports-60-250/29189617.xlsx
@@ -3814,7 +3814,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311295535</t>
+          <t xml:space="preserve">311295532</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
